--- a/output/table_9_commodity_price_indices.xlsx
+++ b/output/table_9_commodity_price_indices.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C9">
         <v>118</v>
@@ -683,116 +683,116 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Q1</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B11">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C11">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="D11">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="E11">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F11">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="G11">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H11">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="I11">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Q2</t>
+          <t>2023 Q1</t>
         </is>
       </c>
       <c r="B12">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C12">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D12">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E12">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F12">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G12">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="H12">
         <v>150</v>
       </c>
       <c r="I12">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Q3</t>
+          <t>2023 Q2</t>
         </is>
       </c>
       <c r="B13">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C13">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E13">
         <v>97</v>
       </c>
       <c r="F13">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G13">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H13">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I13">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Q4</t>
+          <t>2023 Q3</t>
         </is>
       </c>
       <c r="B14">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D14">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E14">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F14">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G14">
         <v>157</v>
@@ -801,224 +801,286 @@
         <v>148</v>
       </c>
       <c r="I14">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Q1</t>
+          <t>2023 Q4</t>
         </is>
       </c>
       <c r="B15">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="D15">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E15">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F15">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G15">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H15">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I15">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Q2</t>
+          <t>2024 Q1</t>
         </is>
       </c>
       <c r="B16">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C16">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="D16">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F16">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="G16">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="H16">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I16">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Q3</t>
+          <t>2024 Q2</t>
         </is>
       </c>
       <c r="B17">
+        <v>133</v>
+      </c>
+      <c r="C17">
+        <v>191</v>
+      </c>
+      <c r="D17">
         <v>126</v>
       </c>
-      <c r="C17">
-        <v>197</v>
-      </c>
-      <c r="D17">
-        <v>120</v>
-      </c>
       <c r="E17">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F17">
         <v>186</v>
       </c>
       <c r="G17">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H17">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I17">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024 Q4</t>
+          <t>2024 Q3</t>
         </is>
       </c>
       <c r="B18">
         <v>126</v>
       </c>
       <c r="C18">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="D18">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F18">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="G18">
         <v>155</v>
       </c>
       <c r="H18">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I18">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025 Q1</t>
+          <t>2024 Q4</t>
         </is>
       </c>
       <c r="B19">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="D19">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E19">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F19">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="G19">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="H19">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I19">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025 Q2</t>
+          <t>2025 Q1</t>
         </is>
       </c>
       <c r="B20">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C20">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D20">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E20">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F20">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="G20">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="H20">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I20">
-        <v>134</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>118</v>
+      </c>
+      <c r="C21">
+        <v>228</v>
+      </c>
+      <c r="D21">
+        <v>125</v>
+      </c>
+      <c r="E21">
+        <v>112</v>
+      </c>
+      <c r="F21">
+        <v>222</v>
+      </c>
+      <c r="G21">
+        <v>153</v>
+      </c>
+      <c r="H21">
+        <v>183</v>
+      </c>
+      <c r="I21">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2025 Q3</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>113</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>202</v>
       </c>
-      <c r="D21">
+      <c r="D22">
         <v>128</v>
       </c>
-      <c r="E21">
-        <v>110</v>
-      </c>
-      <c r="F21">
+      <c r="E22">
+        <v>112</v>
+      </c>
+      <c r="F22">
         <v>234</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>155</v>
       </c>
-      <c r="H21">
-        <v>187</v>
-      </c>
-      <c r="I21">
+      <c r="H22">
+        <v>188</v>
+      </c>
+      <c r="I22">
         <v>136</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>115</v>
+      </c>
+      <c r="C23">
+        <v>204</v>
+      </c>
+      <c r="D23">
+        <v>128</v>
+      </c>
+      <c r="E23">
+        <v>108</v>
+      </c>
+      <c r="F23">
+        <v>275</v>
+      </c>
+      <c r="G23">
+        <v>160</v>
+      </c>
+      <c r="H23">
+        <v>210</v>
+      </c>
+      <c r="I23">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
